--- a/file_upload_forms/041_nostalgic_media_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/041_nostalgic_media_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,11 @@
           <t>First Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter your first name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -551,7 +555,11 @@
           <t>Last Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your last name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -644,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Submission Url</t>
+          <t>Submission URL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -749,7 +757,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -765,47 +773,47 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submission_notes</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submission Notes</t>
+          <t>Submission Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +826,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +849,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_tags_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Tags 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,13 +882,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission Tags</t>
+          <t>Submission Tags 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -897,13 +905,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission Tags</t>
+          <t>Submission Tags 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -920,174 +928,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submission Tags</t>
+          <t>Submission Tags 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submission_tags_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission_tags_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_tags_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_tags_8</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submission_tags_9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission_tags_10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_tags_11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission Tags</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +949,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1140,7 +987,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1004,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1021,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1038,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1055,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>Literature</t>
         </is>
       </c>
     </row>
@@ -1225,24 +1072,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>submission_categories_choices</t>
+          <t>submission_permissions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1254,505 +1101,318 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submission_permissions_choices</t>
+          <t>submission_tags_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_tags_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>in-progress</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>in-progress</t>
+          <t>History</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_tags_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>literature</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>Literature</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_tags_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>submission_tags_2_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>in-progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>In-Progress</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submission_tags_2_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submission_tags_2_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>Archived</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submission_tags_3_choices</t>
+          <t>submission_tags_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>submission_tags_3_choices</t>
+          <t>submission_tags_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>History</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submission_tags_3_choices</t>
+          <t>submission_tags_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>submission_tags_4_choices</t>
+          <t>submission_tags_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>literature</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>Literature</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>submission_tags_4_choices</t>
+          <t>submission_tags_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>submission_tags_5_choices</t>
+          <t>submission_tags_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>in-progress</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>in-progress</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submission_tags_5_choices</t>
+          <t>submission_tags_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>Archived</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>submission_tags_5_choices</t>
+          <t>submission_tags_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>in-progress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>archived</t>
+          <t>In-Progress</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submission_tags_6_choices</t>
+          <t>submission_tags_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>submission_tags_6_choices</t>
+          <t>submission_tags_4_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>submission_tags_6_choices</t>
+          <t>submission_tags_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>literature</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>submission_tags_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>music</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>music</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>submission_tags_7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>etc.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>submission_tags_8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>private</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>private</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>submission_tags_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>submission_tags_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>in-progress</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>in-progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>submission_tags_9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>submission_tags_10_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>submission_tags_10_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>submission_tags_10_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>submission_tags_11_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>archived</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>archived</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>submission_tags_11_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
